--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,18 +596,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MICAELIS Loveseat</t>
+          <t>MICAELIS Loveseat, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Loveseat adds a Transitional touch while keeping the room feeling warm and welcoming. This upholstery motion is made to fit naturally into the room. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22")
+Product Dimensions: 54.5"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
 Size: Black [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Black
 Weight: 167.55 lbs</t>
         </is>
@@ -730,18 +730,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MICAELIS Loveseat</t>
+          <t>MICAELIS Loveseat, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with MICAELIS Loveseat and its Transitional character. Built as a upholstery motion, it pairs well with a wide range of interiors. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.
-Product Dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21")
+Product Dimensions: 54.5"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
 Size: Blue [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Slate Blue
 Weight: 167.55 lbs</t>
         </is>
@@ -864,18 +864,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MICAELIS Recliner</t>
+          <t>MICAELIS Recliner, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Recliner brings a Transitional look to your home with a refined, comfortable feel. As a upholstery motion, it is designed to complement your space. The Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 31" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22")
+Product Dimensions: 31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
 Size: Black [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Black
 Weight: 90.39 lbs</t>
         </is>
@@ -998,18 +998,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MICAELIS Recliner</t>
+          <t>MICAELIS Recliner, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Elevate your space with MICAELIS Recliner, styled in Transitional and designed for everyday comfort. This upholstery motion is made to fit naturally into the room. With Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and Slate Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 31" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22")
+Product Dimensions: 31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
 Size: Blue [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Slate Blue
 Weight: 90.39 lbs</t>
         </is>
@@ -1132,18 +1132,18 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MICAELIS Sofa</t>
+          <t>MICAELIS Sofa, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Sofa adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a upholstery motion, it pairs well with a wide range of interiors. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22")
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
 Size: Black [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Black
 Weight: 205.03 lbs</t>
         </is>
@@ -1266,18 +1266,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MICAELIS Sofa</t>
+          <t>MICAELIS Sofa, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with MICAELIS Sofa and its Transitional character. As a upholstery motion, it is designed to complement your space. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.
-Product Dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21")
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
 Size: Blue [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Slate Blue
 Weight: 205.03 lbs</t>
         </is>
@@ -1400,18 +1400,18 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>OMNUS Trundle w/ 2 Dividers</t>
+          <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, Others, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 74 1 or 4" W x 40 1 or 2"D x 10 3 or 4" H
+OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.
+Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H
 Size: Gray [NOT AVAILABLE]
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer, Others
+Materials: Solid Wood, Wood Veneer.
 Color: Gray
 Weight: 41.8 lbs</t>
         </is>

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,193 +413,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE]</t>
+          <t>FM69007BK-LV-M</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FM69007BK-LV-M</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Loveseat, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>MICAELIS Loveseat, Black [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Loveseat adds a Transitional touch while keeping the room feeling warm and welcoming. This upholstery motion is made to fit naturally into the room. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.
@@ -612,41 +612,44 @@
 Weight: 167.55 lbs</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MICAELIS Loveseat Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MICAELIS Loveseat Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+          <t>The MICAELIS Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The MICAELIS Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Loveseat, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Loveseat, Black [NOT AVAILABLE]</t>
+          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>FM69007BK-LV-M-1.jpg,FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -654,86 +657,88 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
         <v>167.55</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>54.5"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>54.5"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y2" t="n">
+        <v>55.1</v>
+      </c>
       <c r="Z2" t="n">
-        <v>55.1</v>
+        <v>29.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>29.9</v>
+        <v>25.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AC2" t="n">
         <v>24.4</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Slate Blue</t>
+          <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE]</t>
+          <t>FM69007BL-LV-M</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FM69007BL-LV-M</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Loveseat, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>MICAELIS Loveseat, Blue [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with MICAELIS Loveseat and its Transitional character. Built as a upholstery motion, it pairs well with a wide range of interiors. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.
@@ -746,41 +751,44 @@
 Weight: 167.55 lbs</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MICAELIS Loveseat Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MICAELIS Loveseat Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+          <t>The MICAELIS Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The MICAELIS Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Loveseat, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Loveseat, Blue [NOT AVAILABLE]</t>
+          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>FM69007BL-LV-M-1.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -788,86 +796,88 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
         <v>167.55</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>54.5"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.5"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y3" t="n">
+        <v>55.1</v>
+      </c>
       <c r="Z3" t="n">
-        <v>55.1</v>
+        <v>29.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>29.9</v>
+        <v>25.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AC3" t="n">
         <v>24.4</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE]</t>
+          <t>FM69007BK-CH-M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FM69007BK-CH-M</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Recliner, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>MICAELIS Recliner, Black [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Recliner brings a Transitional look to your home with a refined, comfortable feel. As a upholstery motion, it is designed to complement your space. The Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal construction is complemented by Black tones for a polished look.
@@ -880,41 +890,44 @@
 Weight: 90.39 lbs</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MICAELIS Recliner Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MICAELIS Recliner Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+          <t>The MICAELIS Recliner brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The MICAELIS Recliner brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Recliner, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Recliner, Black [NOT AVAILABLE]</t>
+          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>FM69007BK-CH-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -922,86 +935,88 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
         <v>90.39</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="Z4" t="n">
-        <v>32.3</v>
+        <v>29.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.9</v>
+        <v>25.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AC4" t="n">
         <v>14.3</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slate Blue</t>
+          <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE]</t>
+          <t>FM69007BL-CH-M</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FM69007BL-CH-M</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Recliner, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>MICAELIS Recliner, Blue [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Elevate your space with MICAELIS Recliner, styled in Transitional and designed for everyday comfort. This upholstery motion is made to fit naturally into the room. With Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and Slate Blue tones, it blends structure and softness in one clean profile.
@@ -1014,41 +1029,44 @@
 Weight: 90.39 lbs</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MICAELIS Recliner Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MICAELIS Recliner Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+          <t>The MICAELIS Recliner brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The MICAELIS Recliner brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Recliner, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Recliner, Blue [NOT AVAILABLE]</t>
+          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>FM69007BL-CH-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
@@ -1056,86 +1074,88 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
         <v>90.39</v>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y5" t="n">
+        <v>32.3</v>
+      </c>
       <c r="Z5" t="n">
-        <v>32.3</v>
+        <v>29.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>29.9</v>
+        <v>25.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AC5" t="n">
         <v>14.3</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE]</t>
+          <t>FM69007BK-SF-M</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FM69007BK-SF-M</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Sofa, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa, Black [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Sofa adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a upholstery motion, it pairs well with a wide range of interiors. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.
@@ -1148,41 +1168,44 @@
 Weight: 205.03 lbs</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Micaelis Sofa Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Micaelis Sofa Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+          <t>The MICAELIS Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Sofa, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sofa, Black [NOT AVAILABLE]</t>
+          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>FM69007BK-SF-M-1.jpg,FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
@@ -1190,86 +1213,88 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
         <v>205.03</v>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y6" t="n">
+        <v>76</v>
+      </c>
       <c r="Z6" t="n">
-        <v>76</v>
+        <v>29.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>29.9</v>
+        <v>25.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AC6" t="n">
         <v>33.7</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slate Blue</t>
+          <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE]</t>
+          <t>FM69007BL-SF-M</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FM69007BL-SF-M</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Sofa, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa, Blue [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with MICAELIS Sofa and its Transitional character. As a upholstery motion, it is designed to complement your space. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.
@@ -1282,41 +1307,44 @@
 Weight: 205.03 lbs</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Micaelis Sofa Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Micaelis Sofa Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+          <t>The MICAELIS Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Sofa, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sofa, Blue [NOT AVAILABLE]</t>
+          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>FM69007BL-SF-M-1.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -1324,86 +1352,88 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
         <v>205.03</v>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y7" t="n">
+        <v>76</v>
+      </c>
       <c r="Z7" t="n">
-        <v>76</v>
+        <v>29.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>29.9</v>
+        <v>25.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AC7" t="n">
         <v>33.7</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Gray [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gray [NOT AVAILABLE]</t>
+          <t>FM-TR452-GY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FM-TR452-GY</t>
+          <t>Youth</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Youth</t>
+          <t>Trundle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trundle</t>
+          <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.
@@ -1416,89 +1446,99 @@
 Weight: 41.8 lbs</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OMNUS Trundle w/ 2 Dividers Gray [NOT AVAILABLE] in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OMNUS Trundle w/ 2 Dividers Gray [NOT AVAILABLE] in Gray | GOODDEGG</t>
+          <t>The OMNUS Trundle w/ Dividers brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>The OMNUS Trundle w/ Dividers brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OMNUS</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OMNUS</t>
+          <t>Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
+          <t>Gray [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Gray [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>FM-TR452-GY.jpg</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>109</v>
       </c>
       <c r="Q8" t="n">
         <v>109</v>
       </c>
       <c r="R8" t="n">
-        <v>109</v>
+        <v>237</v>
       </c>
       <c r="S8" t="n">
-        <v>237</v>
-      </c>
-      <c r="T8" t="n">
         <v>41.8</v>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>74 1/4"W X 40 1/2"D X 10 3/4"H</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>74 1/4"W X 40 1/2"D X 10 3/4"H</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Solid Wood, Wood Veneer, Others</t>
+          <t>Transitional,Gray,Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Transitional,Gray,Solid Wood, Wood Veneer, Others</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y8" t="n">
+        <v>79.5</v>
+      </c>
       <c r="Z8" t="n">
-        <v>79.5</v>
+        <v>15.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.4</v>
+        <v>5.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC8" t="n">
         <v>3.8</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Youth, Trundle, OMNUS</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,15 +601,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MICAELIS Loveseat adds a Transitional touch while keeping the room feeling warm and welcoming. This upholstery motion is made to fit naturally into the room. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 54.5"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
-Size: Black [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Black
-Weight: 167.55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MICAELIS Loveseat adds a Transitional touch while keeping the room feeling warm and welcoming. This upholstery motion is made to fit naturally into the room. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54.5"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")&lt;br&gt;
+Size: Black [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 167.55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -740,15 +740,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MICAELIS Loveseat and its Transitional character. Built as a upholstery motion, it pairs well with a wide range of interiors. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.
-Product Dimensions: 54.5"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
-Size: Blue [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Slate Blue
-Weight: 167.55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MICAELIS Loveseat and its Transitional character. Built as a upholstery motion, it pairs well with a wide range of interiors. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 54.5"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;br&gt;
+Size: Blue [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Slate Blue&lt;br&gt;
+Weight: 167.55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -879,15 +879,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MICAELIS Recliner brings a Transitional look to your home with a refined, comfortable feel. As a upholstery motion, it is designed to complement your space. The Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
-Size: Black [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Black
-Weight: 90.39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MICAELIS Recliner brings a Transitional look to your home with a refined, comfortable feel. As a upholstery motion, it is designed to complement your space. The Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")&lt;br&gt;
+Size: Black [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 90.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1018,15 +1018,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MICAELIS Recliner, styled in Transitional and designed for everyday comfort. This upholstery motion is made to fit naturally into the room. With Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and Slate Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
-Size: Blue [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Slate Blue
-Weight: 90.39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MICAELIS Recliner, styled in Transitional and designed for everyday comfort. This upholstery motion is made to fit naturally into the room. With Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and Slate Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")&lt;br&gt;
+Size: Blue [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Slate Blue&lt;br&gt;
+Weight: 90.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1157,15 +1157,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MICAELIS Sofa adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a upholstery motion, it pairs well with a wide range of interiors. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
-Size: Black [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Black
-Weight: 205.03 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MICAELIS Sofa adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a upholstery motion, it pairs well with a wide range of interiors. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")&lt;br&gt;
+Size: Black [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 205.03 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1296,15 +1296,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MICAELIS Sofa and its Transitional character. As a upholstery motion, it is designed to complement your space. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.
-Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
-Size: Blue [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Slate Blue
-Weight: 205.03 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MICAELIS Sofa and its Transitional character. As a upholstery motion, it is designed to complement your space. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;br&gt;
+Size: Blue [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Slate Blue&lt;br&gt;
+Weight: 205.03 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1435,15 +1435,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H
-Size: Gray [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 41.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;br&gt;
+Size: Gray [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 41.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -703,7 +718,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -842,7 +872,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -981,7 +1026,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1180,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1334,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1488,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1642,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Youth, Trundle, OMNUS</t>
+          <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -629,12 +629,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MICAELIS Loveseat Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+          <t>MICAELIS Loveseat, Black [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The MICAELIS Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Loveseat, Black [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MICAELIS Loveseat Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+          <t>MICAELIS Loveseat, Blue [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The MICAELIS Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Loveseat, Blue [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MICAELIS Recliner Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+          <t>MICAELIS Recliner, Black [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The MICAELIS Recliner brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Recliner, Black [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MICAELIS Recliner Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+          <t>MICAELIS Recliner, Blue [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The MICAELIS Recliner brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Recliner, Blue [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Micaelis Sofa Black [NOT AVAILABLE] in Black | GOODDEGG</t>
+          <t>MICAELIS Sofa, Black [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Sofa, Black [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Micaelis Sofa Blue [NOT AVAILABLE] in Slate Blue | GOODDEGG</t>
+          <t>MICAELIS Sofa, Blue [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Sofa, Blue [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OMNUS Trundle w/ 2 Dividers Gray [NOT AVAILABLE] in Gray | GOODDEGG</t>
+          <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The OMNUS Trundle w/ Dividers brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/NOT_AVAILABLE_Single items.xlsx
+++ b/FOA Singles/NOT_AVAILABLE_Single items.xlsx
@@ -413,171 +413,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
@@ -586,35 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>micaelis-loveseat-black-not-available</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>FM69007BK-LV-M</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>MICAELIS Loveseat, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MICAELIS Loveseat adds a Transitional touch while keeping the room feeling warm and welcoming. This upholstery motion is made to fit naturally into the room. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
@@ -627,111 +647,117 @@
 Weight: 167.55 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>MICAELIS Loveseat, Black [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>MICAELIS Loveseat, Black [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Loveseat, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>FM69007BK-LV-M-1.jpg,FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>FM69007BK-LV-M-1.jpg,FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>167.55</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>54.5"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>55.1</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>25.6</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>24.4</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
@@ -740,35 +766,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>micaelis-loveseat-blue-not-available</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Slate Blue</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FM69007BL-LV-M</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>MICAELIS Loveseat, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with MICAELIS Loveseat and its Transitional character. Built as a upholstery motion, it pairs well with a wide range of interiors. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.&lt;br&gt;
@@ -781,111 +812,117 @@
 Weight: 167.55 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>MICAELIS Loveseat, Blue [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>MICAELIS Loveseat, Blue [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Loveseat, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>FM69007BL-LV-M-1.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>FM69007BL-LV-M-1.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>167.55</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>54.5"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>55.1</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>25.6</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>24.4</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
@@ -894,35 +931,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>micaelis-recliner-black-not-available</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>FM69007BK-CH-M</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>MICAELIS Recliner, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MICAELIS Recliner brings a Transitional look to your home with a refined, comfortable feel. As a upholstery motion, it is designed to complement your space. The Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
@@ -935,111 +977,117 @@
 Weight: 90.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>MICAELIS Recliner, Black [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>MICAELIS Recliner, Black [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Recliner, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>FM69007BK-CH-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>FM69007BK-CH-M-1.jpg,FM69007BK-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>90.39</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>32.3</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>25.6</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>14.3</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
@@ -1048,35 +1096,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>micaelis-recliner-blue-not-available</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Slate Blue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>FM69007BL-CH-M</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>MICAELIS Recliner, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with MICAELIS Recliner, styled in Transitional and designed for everyday comfort. This upholstery motion is made to fit naturally into the room. With Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and Slate Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
@@ -1089,111 +1142,117 @@
 Weight: 90.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>MICAELIS Recliner, Blue [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>MICAELIS Recliner, Blue [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Recliner, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>FM69007BL-CH-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>FM69007BL-CH-M-1.jpg,FM69007BL-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>90.39</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>31"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>32.3</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>25.6</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>14.3</v>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
@@ -1202,35 +1261,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>micaelis-sofa-black-not-available</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>FM69007BK-SF-M</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>MICAELIS Sofa, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MICAELIS Sofa adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a upholstery motion, it pairs well with a wide range of interiors. Crafted from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
@@ -1243,111 +1307,117 @@
 Weight: 205.03 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>MICAELIS Sofa, Black [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>MICAELIS Sofa, Black [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Sofa, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>FM69007BK-SF-M-1.jpg,FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>FM69007BK-SF-M-1.jpg,FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>205.03</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>76</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>25.6</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>33.7</v>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
@@ -1356,35 +1426,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>micaelis-sofa-blue-not-available</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Slate Blue</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>FM69007BL-SF-M</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>MICAELIS Sofa, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with MICAELIS Sofa and its Transitional character. As a upholstery motion, it is designed to complement your space. Finished in Slate Blue tones, the Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal build balances durability with visual appeal.&lt;br&gt;
@@ -1397,111 +1472,117 @@
 Weight: 205.03 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>MICAELIS Sofa, Blue [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>MICAELIS Sofa, Blue [NOT AVAILABLE] Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Sofa, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>FM69007BL-SF-M-1.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>FM69007BL-SF-M-1.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>205.03</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>76</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>25.6</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>33.7</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
@@ -1510,35 +1591,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>omnus-trundle-w-2-dividers-gray-not-available</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Gray [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FM-TR452-GY</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Trundle</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
@@ -1551,111 +1637,117 @@
 Weight: 41.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT AVAILABLE] | GOODDEGG</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>OMNUS Trundle w/ 2 Dividers, Gray [NOT supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Gray [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>FM-TR452-GY.jpg</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>FM-TR452-GY.jpg</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
         <v>109</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>109</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>237</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>41.8</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>74 1/4"W X 40 1/2"D X 10 3/4"H</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Transitional,Gray,Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>79.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
         <v>15.4</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AD8" t="n">
         <v>5.3</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>3.8</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
